--- a/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_15Jan2025.xlsx
+++ b/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_15Jan2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allyftw\Documents\GitHub\IntelliAudit\Docs\ISO_Controls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82163C78-EB5B-4E5F-9C2E-B10F1803294C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA1BC51-BD0C-477F-A60A-10A7866F18E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="500">
   <si>
     <t>Control ID</t>
   </si>
@@ -1485,15 +1485,6 @@
     <t>5-1_information_security_policy.docx</t>
   </si>
   <si>
-    <t>5-11_Global_Enterprises_Inc._Asset_Inventory.xlsx</t>
-  </si>
-  <si>
-    <t>5-29_business_continuity_plan_example1.docx</t>
-  </si>
-  <si>
-    <t>5-29_business_continuity_plan_example2.docx</t>
-  </si>
-  <si>
     <t>5-30_ICT_Continuity_Plan.docx</t>
   </si>
   <si>
@@ -1503,9 +1494,6 @@
     <t>8-4_Code_Repo_Access_List.png</t>
   </si>
   <si>
-    <t>101 Synthetic Examples of Destruction Certs</t>
-  </si>
-  <si>
     <t>7-7_coverr-a-guy-working-on-a-pc-18-1080p.mp4</t>
   </si>
   <si>
@@ -1527,7 +1515,16 @@
     <t>Syntheticly Generated</t>
   </si>
   <si>
-    <t>Multiple examples spanning compliant, non-compliant, and partially compliant</t>
+    <t>5-29_business_continuity_plan_example1.docx, 5-29_business_continuity_plan_example2.docx</t>
+  </si>
+  <si>
+    <t>101 Synthetic Examples of Destruction Certs (IntelliAudit\Docs\Data\Artifacts\synthetic_data\destruction_certificates)</t>
+  </si>
+  <si>
+    <t>Multiple examples spanning compliant, non-compliant, and partially compliant (IntelliAudit\Docs\Data\Artifacts\synthetic_data\asset_inventory)</t>
+  </si>
+  <si>
+    <t>6-4_Verbal_Warning.txt, 6-4_Written_Warning.txt, 6-4_Termination_Letter.txt</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1610,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1638,7 +1639,7 @@
     <tableColumn id="5" xr3:uid="{84900592-C228-4FBB-905A-9308E9CDBAB3}" name="Status"/>
     <tableColumn id="9" xr3:uid="{25F22B21-FC5F-4914-A030-BABA9DF927D3}" name="Real World Data"/>
     <tableColumn id="7" xr3:uid="{B7FF0A4A-19E5-4EA8-BB48-D67EA8BF8F5B}" name="Expert Crafted"/>
-    <tableColumn id="8" xr3:uid="{8CAE46E2-E21D-4C77-AFAC-ACDDC8295C35}" name="Syntheticly Generated"/>
+    <tableColumn id="8" xr3:uid="{8CAE46E2-E21D-4C77-AFAC-ACDDC8295C35}" name="Syntheticly Generated" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4404,8 +4405,8 @@
     <col min="5" max="5" width="56.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.28515625" customWidth="1"/>
+    <col min="9" max="9" width="70.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4428,13 +4429,13 @@
         <v>460</v>
       </c>
       <c r="G1" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" t="s">
         <v>494</v>
       </c>
-      <c r="H1" t="s">
-        <v>498</v>
-      </c>
-      <c r="I1" t="s">
-        <v>499</v>
+      <c r="I1" s="5" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4457,9 +4458,9 @@
         <v>482</v>
       </c>
       <c r="G2" t="s">
-        <v>495</v>
-      </c>
-      <c r="I2" t="s">
+        <v>491</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>485</v>
       </c>
     </row>
@@ -4483,10 +4484,10 @@
         <v>482</v>
       </c>
       <c r="G3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4509,10 +4510,10 @@
         <v>481</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
@@ -4531,8 +4532,8 @@
       <c r="F5" t="s">
         <v>481</v>
       </c>
-      <c r="H5" t="s">
-        <v>486</v>
+      <c r="I5" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4614,11 +4615,11 @@
       <c r="F9" t="s">
         <v>481</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" s="5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>76</v>
       </c>
@@ -4637,11 +4638,8 @@
       <c r="F10" t="s">
         <v>481</v>
       </c>
-      <c r="H10" t="s">
-        <v>487</v>
-      </c>
-      <c r="I10" t="s">
-        <v>488</v>
+      <c r="I10" s="5" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4663,11 +4661,11 @@
       <c r="F11" t="s">
         <v>481</v>
       </c>
-      <c r="H11" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -4685,6 +4683,9 @@
       </c>
       <c r="F12" t="s">
         <v>481</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -4707,10 +4708,10 @@
         <v>481</v>
       </c>
       <c r="G13" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>146</v>
       </c>
@@ -4729,8 +4730,8 @@
       <c r="F14" t="s">
         <v>481</v>
       </c>
-      <c r="I14" t="s">
-        <v>492</v>
+      <c r="I14" s="5" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4752,8 +4753,8 @@
       <c r="F15" t="s">
         <v>481</v>
       </c>
-      <c r="H15" t="s">
-        <v>490</v>
+      <c r="G15" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4775,8 +4776,8 @@
       <c r="F16" t="s">
         <v>481</v>
       </c>
-      <c r="H16" t="s">
-        <v>491</v>
+      <c r="G16" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_15Jan2025.xlsx
+++ b/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_15Jan2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allyftw\Documents\GitHub\IntelliAudit\Docs\ISO_Controls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA1BC51-BD0C-477F-A60A-10A7866F18E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE937CE-6A99-4C2C-8471-52B5ED4D6DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="500">
   <si>
     <t>Control ID</t>
   </si>
@@ -1386,9 +1386,6 @@
     <t>Org Chart (PDF)</t>
   </si>
   <si>
-    <t>Asset Inventiry (XLS)</t>
-  </si>
-  <si>
     <t>Information Security Policy (DOC)</t>
   </si>
   <si>
@@ -1476,12 +1473,6 @@
     <t>Data Generated, Dev Build Completed</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>5-27_nist_incident_response_report.docx</t>
-  </si>
-  <si>
     <t>5-1_information_security_policy.docx</t>
   </si>
   <si>
@@ -1525,6 +1516,15 @@
   </si>
   <si>
     <t>6-4_Verbal_Warning.txt, 6-4_Written_Warning.txt, 6-4_Termination_Letter.txt</t>
+  </si>
+  <si>
+    <t>5024_Incident_Management_Policy.docx</t>
+  </si>
+  <si>
+    <t>Asset Inventory (XLS)</t>
+  </si>
+  <si>
+    <t>5-27_incident_response_report.docx</t>
   </si>
 </sst>
 </file>
@@ -2353,7 +2353,7 @@
         <v>315</v>
       </c>
       <c r="H16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3514,7 +3514,7 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F61" t="s">
         <v>151</v>
@@ -3540,7 +3540,7 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F62" t="s">
         <v>154</v>
@@ -3566,7 +3566,7 @@
         <v>55</v>
       </c>
       <c r="E63" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F63" t="s">
         <v>374</v>
@@ -3592,7 +3592,7 @@
         <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F64" t="s">
         <v>375</v>
@@ -3618,7 +3618,7 @@
         <v>64</v>
       </c>
       <c r="E65" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F65" t="s">
         <v>376</v>
@@ -3644,7 +3644,7 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F66" t="s">
         <v>377</v>
@@ -3670,7 +3670,7 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F67" t="s">
         <v>165</v>
@@ -3696,7 +3696,7 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F68" t="s">
         <v>378</v>
@@ -3722,7 +3722,7 @@
         <v>41</v>
       </c>
       <c r="E69" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F69" t="s">
         <v>379</v>
@@ -3748,7 +3748,7 @@
         <v>55</v>
       </c>
       <c r="E70" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F70" t="s">
         <v>380</v>
@@ -3774,7 +3774,7 @@
         <v>21</v>
       </c>
       <c r="E71" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F71" t="s">
         <v>381</v>
@@ -3800,7 +3800,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F72" t="s">
         <v>382</v>
@@ -3826,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F73" t="s">
         <v>383</v>
@@ -3852,7 +3852,7 @@
         <v>55</v>
       </c>
       <c r="E74" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F74" t="s">
         <v>384</v>
@@ -3878,7 +3878,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F75" t="s">
         <v>385</v>
@@ -3904,7 +3904,7 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F76" t="s">
         <v>404</v>
@@ -3930,7 +3930,7 @@
         <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F77" t="s">
         <v>386</v>
@@ -3956,7 +3956,7 @@
         <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F78" t="s">
         <v>387</v>
@@ -3982,7 +3982,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F79" t="s">
         <v>388</v>
@@ -4008,7 +4008,7 @@
         <v>55</v>
       </c>
       <c r="E80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F80" t="s">
         <v>389</v>
@@ -4034,7 +4034,7 @@
         <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F81" t="s">
         <v>390</v>
@@ -4060,7 +4060,7 @@
         <v>55</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F82" t="s">
         <v>391</v>
@@ -4086,7 +4086,7 @@
         <v>55</v>
       </c>
       <c r="E83" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F83" t="s">
         <v>198</v>
@@ -4112,7 +4112,7 @@
         <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F84" t="s">
         <v>392</v>
@@ -4138,7 +4138,7 @@
         <v>55</v>
       </c>
       <c r="E85" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F85" t="s">
         <v>203</v>
@@ -4164,7 +4164,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F86" t="s">
         <v>435</v>
@@ -4190,7 +4190,7 @@
         <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F87" t="s">
         <v>437</v>
@@ -4216,7 +4216,7 @@
         <v>55</v>
       </c>
       <c r="E88" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F88" t="s">
         <v>210</v>
@@ -4242,7 +4242,7 @@
         <v>55</v>
       </c>
       <c r="E89" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F89" t="s">
         <v>213</v>
@@ -4268,7 +4268,7 @@
         <v>41</v>
       </c>
       <c r="E90" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F90" t="s">
         <v>393</v>
@@ -4294,7 +4294,7 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F91" t="s">
         <v>218</v>
@@ -4320,7 +4320,7 @@
         <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F92" t="s">
         <v>394</v>
@@ -4346,7 +4346,7 @@
         <v>41</v>
       </c>
       <c r="E93" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F93" t="s">
         <v>444</v>
@@ -4372,7 +4372,7 @@
         <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F94" t="s">
         <v>395</v>
@@ -4417,7 +4417,7 @@
         <v>448</v>
       </c>
       <c r="C1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D1" t="s">
         <v>449</v>
@@ -4426,16 +4426,16 @@
         <v>450</v>
       </c>
       <c r="F1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4446,22 +4446,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D2" t="s">
         <v>450</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>482</v>
-      </c>
-      <c r="G2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4472,7 +4472,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D3" t="s">
         <v>451</v>
@@ -4481,13 +4481,13 @@
         <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4504,13 +4504,13 @@
         <v>450</v>
       </c>
       <c r="E4" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="F4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4527,13 +4527,13 @@
         <v>450</v>
       </c>
       <c r="E5" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="F5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4550,10 +4550,13 @@
         <v>450</v>
       </c>
       <c r="E6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F6" t="s">
-        <v>483</v>
+        <v>480</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4570,10 +4573,13 @@
         <v>450</v>
       </c>
       <c r="E7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F7" t="s">
-        <v>483</v>
+        <v>480</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4590,10 +4596,13 @@
         <v>450</v>
       </c>
       <c r="E8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F8" t="s">
-        <v>483</v>
+        <v>480</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4610,13 +4619,13 @@
         <v>450</v>
       </c>
       <c r="E9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4633,13 +4642,13 @@
         <v>450</v>
       </c>
       <c r="E10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4656,13 +4665,13 @@
         <v>450</v>
       </c>
       <c r="E11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4670,22 +4679,22 @@
         <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C12">
         <v>5.0999999999999996</v>
       </c>
       <c r="D12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -4699,16 +4708,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G13" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4725,13 +4734,13 @@
         <v>450</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F14" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4745,16 +4754,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E15" t="s">
         <v>463</v>
       </c>
-      <c r="E15" t="s">
-        <v>464</v>
-      </c>
       <c r="F15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G15" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4768,16 +4777,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D16" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -15691,26 +15700,26 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B2" t="s">
         <v>475</v>
-      </c>
-      <c r="B2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" t="s">
         <v>477</v>
-      </c>
-      <c r="B3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B4" t="s">
         <v>479</v>
-      </c>
-      <c r="B4" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
